--- a/resources/templates/standard/J3100-02.xlsx
+++ b/resources/templates/standard/J3100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>사양 변경 접수 대장</t>
   </si>
@@ -534,12 +537,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -687,42 +692,42 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
@@ -736,23 +741,23 @@
       <c r="AH4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
       <c r="AN4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR4" s="4"/>
       <c r="AS4" s="4"/>
       <c r="AT4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU4" s="4"/>
       <c r="AV4" s="4"/>
@@ -794,7 +799,7 @@
       <c r="AH5" s="6"/>
       <c r="AI5" s="6"/>
       <c r="AJ5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="7"/>
@@ -846,7 +851,7 @@
       <c r="AH6" s="6"/>
       <c r="AI6" s="6"/>
       <c r="AJ6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="7"/>
@@ -898,7 +903,7 @@
       <c r="AH7" s="6"/>
       <c r="AI7" s="6"/>
       <c r="AJ7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK7" s="7"/>
       <c r="AL7" s="7"/>
@@ -950,7 +955,7 @@
       <c r="AH8" s="6"/>
       <c r="AI8" s="6"/>
       <c r="AJ8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK8" s="7"/>
       <c r="AL8" s="7"/>
@@ -1002,7 +1007,7 @@
       <c r="AH9" s="6"/>
       <c r="AI9" s="6"/>
       <c r="AJ9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK9" s="7"/>
       <c r="AL9" s="7"/>
@@ -1054,7 +1059,7 @@
       <c r="AH10" s="6"/>
       <c r="AI10" s="6"/>
       <c r="AJ10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK10" s="7"/>
       <c r="AL10" s="7"/>
@@ -1106,7 +1111,7 @@
       <c r="AH11" s="6"/>
       <c r="AI11" s="6"/>
       <c r="AJ11" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK11" s="7"/>
       <c r="AL11" s="7"/>
@@ -1158,7 +1163,7 @@
       <c r="AH12" s="6"/>
       <c r="AI12" s="6"/>
       <c r="AJ12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK12" s="7"/>
       <c r="AL12" s="7"/>
@@ -1210,7 +1215,7 @@
       <c r="AH13" s="6"/>
       <c r="AI13" s="6"/>
       <c r="AJ13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK13" s="7"/>
       <c r="AL13" s="7"/>
@@ -1262,7 +1267,7 @@
       <c r="AH14" s="9"/>
       <c r="AI14" s="9"/>
       <c r="AJ14" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK14" s="10"/>
       <c r="AL14" s="10"/>
